--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07319999999999999</v>
+        <v>0.04155</v>
       </c>
       <c r="E2">
-        <v>0.06108000000000001</v>
+        <v>0.0605</v>
       </c>
       <c r="G2">
-        <v>0.09943495038588755</v>
+        <v>0.1415389553077108</v>
       </c>
       <c r="H2">
-        <v>0.09943495038588755</v>
+        <v>0.1415389553077108</v>
       </c>
       <c r="I2">
-        <v>0.09399117971334069</v>
+        <v>0.07927465297279948</v>
       </c>
       <c r="J2">
-        <v>0.0837929661195492</v>
+        <v>0.06876739253984847</v>
       </c>
       <c r="K2">
-        <v>110.154</v>
+        <v>102.2</v>
       </c>
       <c r="L2">
-        <v>0.07590545755237045</v>
+        <v>0.08200272807510231</v>
       </c>
       <c r="M2">
-        <v>46.8006</v>
+        <v>62.18</v>
       </c>
       <c r="N2">
-        <v>0.04161532989507381</v>
+        <v>0.06135780540753898</v>
       </c>
       <c r="O2">
-        <v>0.4248651887357699</v>
+        <v>0.6084148727984344</v>
       </c>
       <c r="P2">
-        <v>46.7456</v>
+        <v>62.18</v>
       </c>
       <c r="Q2">
-        <v>0.04156642361728615</v>
+        <v>0.06135780540753898</v>
       </c>
       <c r="R2">
-        <v>0.4243658877571401</v>
+        <v>0.6084148727984344</v>
       </c>
       <c r="S2">
-        <v>0.05499999999999972</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.001175198608564841</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>701.8000000000001</v>
+        <v>565.5</v>
       </c>
       <c r="V2">
-        <v>0.6240441045705141</v>
+        <v>0.5580224985198342</v>
       </c>
       <c r="W2">
-        <v>0.07675983584443385</v>
+        <v>0.08832981975406304</v>
       </c>
       <c r="X2">
-        <v>0.05283271689989084</v>
+        <v>0.08706260720893201</v>
       </c>
       <c r="Y2">
-        <v>0.02392711894454301</v>
+        <v>0.001267212545131027</v>
       </c>
       <c r="Z2">
-        <v>2.489116974089994</v>
+        <v>1.949878592169821</v>
       </c>
       <c r="AA2">
-        <v>0.1178279494570444</v>
+        <v>0.126710686947602</v>
       </c>
       <c r="AB2">
-        <v>0.05273273909276544</v>
+        <v>0.08692293734099707</v>
       </c>
       <c r="AC2">
-        <v>0.06509529279142375</v>
+        <v>0.03979076548196123</v>
       </c>
       <c r="AD2">
-        <v>4.268</v>
+        <v>3.389</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.268</v>
+        <v>3.389</v>
       </c>
       <c r="AG2">
-        <v>-697.532</v>
+        <v>-562.111</v>
       </c>
       <c r="AH2">
-        <v>0.003780778620706761</v>
+        <v>0.003333041565162487</v>
       </c>
       <c r="AI2">
-        <v>0.003182775427899845</v>
+        <v>0.002914043039100113</v>
       </c>
       <c r="AJ2">
-        <v>-1.633304298144558</v>
+        <v>-1.245567696088316</v>
       </c>
       <c r="AK2">
-        <v>-1.091312456193051</v>
+        <v>-0.9407888680795798</v>
       </c>
       <c r="AL2">
-        <v>0.264</v>
+        <v>0.295</v>
       </c>
       <c r="AM2">
-        <v>0.264</v>
+        <v>0.295</v>
       </c>
       <c r="AN2">
-        <v>0.02994247228848043</v>
+        <v>0.0324616858237548</v>
       </c>
       <c r="AO2">
-        <v>516.6666666666666</v>
+        <v>334.9152542372881</v>
       </c>
       <c r="AP2">
-        <v>-4.893587764837941</v>
+        <v>-5.384204980842912</v>
       </c>
       <c r="AQ2">
-        <v>516.6666666666666</v>
+        <v>334.9152542372881</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.075</v>
+        <v>0.0555</v>
       </c>
       <c r="E3">
-        <v>0.123</v>
+        <v>0.124</v>
       </c>
       <c r="G3">
-        <v>0.1201827875095202</v>
+        <v>0.1822495606326889</v>
       </c>
       <c r="H3">
-        <v>0.1201827875095202</v>
+        <v>0.1822495606326889</v>
       </c>
       <c r="I3">
-        <v>0.1465346534653465</v>
+        <v>0.09964850615114236</v>
       </c>
       <c r="J3">
-        <v>0.1255543003964826</v>
+        <v>0.08057762601321777</v>
       </c>
       <c r="K3">
-        <v>76.7</v>
+        <v>63.8</v>
       </c>
       <c r="L3">
-        <v>0.1168316831683168</v>
+        <v>0.1121265377855887</v>
       </c>
       <c r="M3">
-        <v>22.155</v>
+        <v>31.8</v>
       </c>
       <c r="N3">
-        <v>0.04094437257438551</v>
+        <v>0.06329617834394904</v>
       </c>
       <c r="O3">
-        <v>0.2888526727509778</v>
+        <v>0.4984326018808778</v>
       </c>
       <c r="P3">
-        <v>22.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q3">
-        <v>0.04084272777675106</v>
+        <v>0.06329617834394904</v>
       </c>
       <c r="R3">
-        <v>0.288135593220339</v>
+        <v>0.4984326018808778</v>
       </c>
       <c r="S3">
-        <v>0.05499999999999972</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.002482509591514318</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>396.6</v>
+        <v>313.1</v>
       </c>
       <c r="V3">
-        <v>0.7329513953058584</v>
+        <v>0.6232085987261147</v>
       </c>
       <c r="W3">
-        <v>0.1807683242988452</v>
+        <v>0.1229523993062247</v>
       </c>
       <c r="X3">
-        <v>0.05280062543219093</v>
+        <v>0.08702399111590897</v>
       </c>
       <c r="Y3">
-        <v>0.1279676988666542</v>
+        <v>0.03592840819031573</v>
       </c>
       <c r="Z3">
-        <v>10.04129703273172</v>
+        <v>4.606168542054562</v>
       </c>
       <c r="AA3">
-        <v>1.260728024017908</v>
+        <v>0.3711541261355211</v>
       </c>
       <c r="AB3">
-        <v>0.05273256452553629</v>
+        <v>0.08692764012713726</v>
       </c>
       <c r="AC3">
-        <v>1.207995459492372</v>
+        <v>0.2842264860083838</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AG3">
-        <v>-395.37</v>
+        <v>-311.98</v>
       </c>
       <c r="AH3">
-        <v>0.002267991813102723</v>
+        <v>0.002224340641881157</v>
       </c>
       <c r="AI3">
-        <v>0.002364793417030358</v>
+        <v>0.002471206036803319</v>
       </c>
       <c r="AJ3">
-        <v>-2.713030947642901</v>
+        <v>-1.638378321604874</v>
       </c>
       <c r="AK3">
-        <v>-3.200599044766454</v>
+        <v>-2.226520125606623</v>
       </c>
       <c r="AL3">
-        <v>0.031</v>
+        <v>0.023</v>
       </c>
       <c r="AM3">
-        <v>0.031</v>
+        <v>0.023</v>
       </c>
       <c r="AN3">
-        <v>0.01248730964467005</v>
+        <v>0.01904761904761905</v>
       </c>
       <c r="AO3">
-        <v>3103.225806451613</v>
+        <v>2465.217391304348</v>
       </c>
       <c r="AP3">
-        <v>-4.013908629441625</v>
+        <v>-5.305782312925171</v>
       </c>
       <c r="AQ3">
-        <v>3103.225806451613</v>
+        <v>2465.217391304348</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Union Insurance Co., Ltd. (TWSE:2816)</t>
+          <t>Taiwan Fire &amp; Marine Insurance Co., Ltd. (TWSE:2832)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07139999999999999</v>
+        <v>0.0464</v>
       </c>
       <c r="E4">
-        <v>0.207</v>
+        <v>0.0605</v>
       </c>
       <c r="G4">
-        <v>0.08373435996150146</v>
+        <v>0.08455696202531646</v>
       </c>
       <c r="H4">
-        <v>0.08373435996150146</v>
+        <v>0.08455696202531646</v>
       </c>
       <c r="I4">
-        <v>0.06288097529675971</v>
+        <v>0.1893670886075949</v>
       </c>
       <c r="J4">
-        <v>0.05374901456270767</v>
+        <v>0.1553792691664676</v>
       </c>
       <c r="K4">
-        <v>17</v>
+        <v>34.7</v>
       </c>
       <c r="L4">
-        <v>0.05453962143086301</v>
+        <v>0.1756962025316456</v>
       </c>
       <c r="M4">
-        <v>6.43</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N4">
-        <v>0.04069620253164557</v>
+        <v>0.03546246370800498</v>
       </c>
       <c r="O4">
-        <v>0.3782352941176471</v>
+        <v>0.2463976945244957</v>
       </c>
       <c r="P4">
-        <v>6.43</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.04069620253164557</v>
+        <v>0.03546246370800498</v>
       </c>
       <c r="R4">
-        <v>0.3782352941176471</v>
+        <v>0.2463976945244957</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>81.40000000000001</v>
+        <v>106.4</v>
       </c>
       <c r="V4">
-        <v>0.5151898734177216</v>
+        <v>0.4413106594773953</v>
       </c>
       <c r="W4">
-        <v>0.08542713567839195</v>
+        <v>0.1016403046280024</v>
       </c>
       <c r="X4">
-        <v>0.05286480836759076</v>
+        <v>0.08719689962759444</v>
       </c>
       <c r="Y4">
-        <v>0.03256232731080119</v>
+        <v>0.01444340500040792</v>
       </c>
       <c r="Z4">
-        <v>2.566086820505643</v>
+        <v>1.076059714503651</v>
       </c>
       <c r="AA4">
-        <v>0.13792463788453</v>
+        <v>0.167197372019055</v>
       </c>
       <c r="AB4">
-        <v>0.05273291365999459</v>
+        <v>0.08690663476483718</v>
       </c>
       <c r="AC4">
-        <v>0.08519172422453546</v>
+        <v>0.08029073725421787</v>
       </c>
       <c r="AD4">
-        <v>0.696</v>
+        <v>1.62</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.696</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>-80.70400000000001</v>
+        <v>-104.78</v>
       </c>
       <c r="AH4">
-        <v>0.004385743812068357</v>
+        <v>0.006674357284113382</v>
       </c>
       <c r="AI4">
-        <v>0.003185413005272407</v>
+        <v>0.005190311418685122</v>
       </c>
       <c r="AJ4">
-        <v>-1.044090250465742</v>
+        <v>-0.7686326291079812</v>
       </c>
       <c r="AK4">
-        <v>-0.5886677948299003</v>
+        <v>-0.5093330740812755</v>
       </c>
       <c r="AL4">
-        <v>0.166</v>
+        <v>0.051</v>
       </c>
       <c r="AM4">
-        <v>0.166</v>
+        <v>0.051</v>
       </c>
       <c r="AN4">
-        <v>0.03237209302325581</v>
+        <v>0.04229765013054831</v>
       </c>
       <c r="AO4">
-        <v>118.0722891566265</v>
+        <v>733.3333333333334</v>
       </c>
       <c r="AP4">
-        <v>-3.753674418604652</v>
+        <v>-2.735770234986945</v>
       </c>
       <c r="AQ4">
-        <v>118.0722891566265</v>
+        <v>733.3333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -990,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0305</v>
+        <v>0.0299</v>
       </c>
       <c r="E5">
-        <v>-0.00084</v>
+        <v>0.0256</v>
       </c>
       <c r="G5">
-        <v>0.04146868250539957</v>
+        <v>0.1174825174825175</v>
       </c>
       <c r="H5">
-        <v>0.04146868250539957</v>
+        <v>0.1174825174825175</v>
       </c>
       <c r="I5">
-        <v>0.08466522678185746</v>
+        <v>0.09324009324009325</v>
       </c>
       <c r="J5">
-        <v>0.07233759760757602</v>
+        <v>0.07838626020444203</v>
       </c>
       <c r="K5">
-        <v>15.6</v>
+        <v>19.4</v>
       </c>
       <c r="L5">
-        <v>0.06738660907127429</v>
+        <v>0.09044289044289043</v>
       </c>
       <c r="M5">
-        <v>3.9156</v>
+        <v>14.8</v>
       </c>
       <c r="N5">
-        <v>0.02461093651791326</v>
+        <v>0.09554551323434474</v>
       </c>
       <c r="O5">
-        <v>0.251</v>
+        <v>0.7628865979381444</v>
       </c>
       <c r="P5">
-        <v>3.9156</v>
+        <v>14.8</v>
       </c>
       <c r="Q5">
-        <v>0.02461093651791326</v>
+        <v>0.09554551323434474</v>
       </c>
       <c r="R5">
-        <v>0.251</v>
+        <v>0.7628865979381444</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1038,73 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>63.8</v>
+        <v>57.5</v>
       </c>
       <c r="V5">
-        <v>0.4010056568196103</v>
+        <v>0.3712072304712718</v>
       </c>
       <c r="W5">
-        <v>0.06809253601047577</v>
+        <v>0.07501933488012373</v>
       </c>
       <c r="X5">
-        <v>0.05277041414223767</v>
+        <v>0.08697841533708447</v>
       </c>
       <c r="Y5">
-        <v>0.01532212186823809</v>
+        <v>-0.01195908045696074</v>
       </c>
       <c r="Z5">
-        <v>1.351043776152764</v>
+        <v>1.09998871806443</v>
       </c>
       <c r="AA5">
-        <v>0.09773126102955866</v>
+        <v>0.08622400187614904</v>
       </c>
       <c r="AB5">
-        <v>0.05273239967124663</v>
+        <v>0.08693320816644445</v>
       </c>
       <c r="AC5">
-        <v>0.04499886135831203</v>
+        <v>-0.0007092062902954166</v>
       </c>
       <c r="AD5">
-        <v>0.202</v>
+        <v>0.162</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.202</v>
+        <v>0.162</v>
       </c>
       <c r="AG5">
-        <v>-63.598</v>
+        <v>-57.338</v>
       </c>
       <c r="AH5">
-        <v>0.001268031788678108</v>
+        <v>0.001044743392965394</v>
       </c>
       <c r="AI5">
-        <v>0.0007805194704832265</v>
+        <v>0.0007011105244479836</v>
       </c>
       <c r="AJ5">
-        <v>-0.6659336977236079</v>
+        <v>-0.5877083290625448</v>
       </c>
       <c r="AK5">
-        <v>-0.3261402447154388</v>
+        <v>-0.3303603323308097</v>
       </c>
       <c r="AL5">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AM5">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AN5">
-        <v>0.009853658536585366</v>
+        <v>0.007751196172248805</v>
       </c>
       <c r="AO5">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="AP5">
-        <v>-3.102341463414634</v>
+        <v>-2.743444976076555</v>
       </c>
       <c r="AQ5">
-        <v>2800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taiwan Fire &amp; Marine Insurance Co., Ltd. (TWSE:2832)</t>
+          <t>Union Insurance Co., Ltd. (TWSE:2816)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,46 +1124,43 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.08800000000000001</v>
-      </c>
-      <c r="E6">
-        <v>-0.467</v>
+        <v>0.0367</v>
       </c>
       <c r="G6">
-        <v>0.1180914512922465</v>
+        <v>0.1160949868073879</v>
       </c>
       <c r="H6">
-        <v>0.1180914512922465</v>
+        <v>0.1160949868073879</v>
       </c>
       <c r="I6">
-        <v>0.003976143141153081</v>
+        <v>-0.05767056162834527</v>
       </c>
       <c r="J6">
-        <v>0.003976143141153081</v>
+        <v>-0.05767056162834527</v>
       </c>
       <c r="K6">
-        <v>0.854</v>
+        <v>-15.7</v>
       </c>
       <c r="L6">
-        <v>0.003395626242544731</v>
+        <v>-0.05917828872973991</v>
       </c>
       <c r="M6">
-        <v>14.3</v>
+        <v>7.03</v>
       </c>
       <c r="N6">
-        <v>0.05367867867867868</v>
+        <v>0.0611304347826087</v>
       </c>
       <c r="O6">
-        <v>16.74473067915691</v>
+        <v>-0.4477707006369427</v>
       </c>
       <c r="P6">
-        <v>14.3</v>
+        <v>7.03</v>
       </c>
       <c r="Q6">
-        <v>0.05367867867867868</v>
+        <v>0.0611304347826087</v>
       </c>
       <c r="R6">
-        <v>16.74473067915691</v>
+        <v>-0.4477707006369427</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1172,73 +1169,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>160</v>
+        <v>88.5</v>
       </c>
       <c r="V6">
-        <v>0.6006006006006006</v>
+        <v>0.7695652173913043</v>
       </c>
       <c r="W6">
-        <v>0.002667916276163698</v>
+        <v>-0.07208448117539026</v>
       </c>
       <c r="X6">
-        <v>0.05297403112671019</v>
+        <v>0.08710122330195505</v>
       </c>
       <c r="Y6">
-        <v>-0.05030611485054649</v>
+        <v>-0.1591857044773453</v>
       </c>
       <c r="Z6">
-        <v>1.118672715950538</v>
+        <v>1.935140339616036</v>
       </c>
       <c r="AA6">
-        <v>0.004448002846721821</v>
+        <v>-0.1116006302153236</v>
       </c>
       <c r="AB6">
-        <v>0.05273350440167318</v>
+        <v>0.08691823455485689</v>
       </c>
       <c r="AC6">
-        <v>-0.04828550155495136</v>
+        <v>-0.1985188647701805</v>
       </c>
       <c r="AD6">
-        <v>2.14</v>
+        <v>0.487</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.14</v>
+        <v>0.487</v>
       </c>
       <c r="AG6">
-        <v>-157.86</v>
+        <v>-88.01300000000001</v>
       </c>
       <c r="AH6">
-        <v>0.007969017651001714</v>
+        <v>0.004216924848684267</v>
       </c>
       <c r="AI6">
-        <v>0.006229260057053037</v>
+        <v>0.002923397383949528</v>
       </c>
       <c r="AJ6">
-        <v>-1.454394693200664</v>
+        <v>-3.261311001593361</v>
       </c>
       <c r="AK6">
-        <v>-0.860084995096437</v>
+        <v>-1.12711462855533</v>
       </c>
       <c r="AL6">
-        <v>0.06</v>
+        <v>0.216</v>
       </c>
       <c r="AM6">
-        <v>0.06</v>
+        <v>0.216</v>
       </c>
       <c r="AN6">
-        <v>1.049019607843137</v>
+        <v>-0.03580882352941177</v>
       </c>
       <c r="AO6">
-        <v>16.66666666666667</v>
+        <v>-70.83333333333334</v>
       </c>
       <c r="AP6">
-        <v>-77.38235294117648</v>
+        <v>6.471544117647059</v>
       </c>
       <c r="AQ6">
-        <v>16.66666666666667</v>
+        <v>-70.83333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04155</v>
+        <v>0.0583</v>
       </c>
       <c r="E2">
-        <v>0.0605</v>
+        <v>0.01705</v>
       </c>
       <c r="G2">
-        <v>0.1415389553077108</v>
+        <v>0.04906713677097106</v>
       </c>
       <c r="H2">
-        <v>0.1415389553077108</v>
+        <v>0.04906713677097106</v>
       </c>
       <c r="I2">
-        <v>0.07927465297279948</v>
+        <v>0.124063464081093</v>
       </c>
       <c r="J2">
-        <v>0.06876739253984847</v>
+        <v>0.1046481005903845</v>
       </c>
       <c r="K2">
-        <v>102.2</v>
+        <v>143.7</v>
       </c>
       <c r="L2">
-        <v>0.08200272807510231</v>
+        <v>0.1055531070956368</v>
       </c>
       <c r="M2">
-        <v>62.18</v>
+        <v>42.94</v>
       </c>
       <c r="N2">
-        <v>0.06135780540753898</v>
+        <v>0.02909017004268004</v>
       </c>
       <c r="O2">
-        <v>0.6084148727984344</v>
+        <v>0.2988169798190675</v>
       </c>
       <c r="P2">
-        <v>62.18</v>
+        <v>42.94</v>
       </c>
       <c r="Q2">
-        <v>0.06135780540753898</v>
+        <v>0.02909017004268004</v>
       </c>
       <c r="R2">
-        <v>0.6084148727984344</v>
+        <v>0.2988169798190675</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>565.5</v>
+        <v>593.1</v>
       </c>
       <c r="V2">
-        <v>0.5580224985198342</v>
+        <v>0.4018020459318475</v>
       </c>
       <c r="W2">
-        <v>0.08832981975406304</v>
+        <v>0.09505846447971412</v>
       </c>
       <c r="X2">
-        <v>0.08706260720893201</v>
+        <v>0.07500934214046437</v>
       </c>
       <c r="Y2">
-        <v>0.001267212545131027</v>
+        <v>0.02004912233924976</v>
       </c>
       <c r="Z2">
-        <v>1.949878592169821</v>
+        <v>2.278535671786426</v>
       </c>
       <c r="AA2">
-        <v>0.126710686947602</v>
+        <v>0.1720838825065371</v>
       </c>
       <c r="AB2">
-        <v>0.08692293734099707</v>
+        <v>0.07495967730196235</v>
       </c>
       <c r="AC2">
-        <v>0.03979076548196123</v>
+        <v>0.09713577814688001</v>
       </c>
       <c r="AD2">
-        <v>3.389</v>
+        <v>3.514</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.389</v>
+        <v>3.514</v>
       </c>
       <c r="AG2">
-        <v>-562.111</v>
+        <v>-589.586</v>
       </c>
       <c r="AH2">
-        <v>0.003333041565162487</v>
+        <v>0.002374943735325565</v>
       </c>
       <c r="AI2">
-        <v>0.002914043039100113</v>
+        <v>0.002731412172739668</v>
       </c>
       <c r="AJ2">
-        <v>-1.245567696088316</v>
+        <v>-0.6650611270662393</v>
       </c>
       <c r="AK2">
-        <v>-0.9407888680795798</v>
+        <v>-0.8502654979564878</v>
       </c>
       <c r="AL2">
-        <v>0.295</v>
+        <v>0.284</v>
       </c>
       <c r="AM2">
-        <v>0.295</v>
+        <v>0.284</v>
       </c>
       <c r="AN2">
-        <v>0.0324616858237548</v>
+        <v>0.02013753581661891</v>
       </c>
       <c r="AO2">
-        <v>334.9152542372881</v>
+        <v>594.7183098591548</v>
       </c>
       <c r="AP2">
-        <v>-5.384204980842912</v>
+        <v>-3.378716332378223</v>
       </c>
       <c r="AQ2">
-        <v>334.9152542372881</v>
+        <v>594.7183098591548</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0555</v>
+        <v>0.0616</v>
       </c>
       <c r="E3">
-        <v>0.124</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1822495606326889</v>
+        <v>0.1047479197258933</v>
       </c>
       <c r="H3">
-        <v>0.1822495606326889</v>
+        <v>0.1047479197258933</v>
       </c>
       <c r="I3">
-        <v>0.09964850615114236</v>
+        <v>0.1584271496165769</v>
       </c>
       <c r="J3">
-        <v>0.08057762601321777</v>
+        <v>0.1313863710675628</v>
       </c>
       <c r="K3">
-        <v>63.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L3">
-        <v>0.1121265377855887</v>
+        <v>0.134769130363844</v>
       </c>
       <c r="M3">
-        <v>31.8</v>
+        <v>24.9</v>
       </c>
       <c r="N3">
-        <v>0.06329617834394904</v>
+        <v>0.03545493378897907</v>
       </c>
       <c r="O3">
-        <v>0.4984326018808778</v>
+        <v>0.3014527845036319</v>
       </c>
       <c r="P3">
-        <v>31.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q3">
-        <v>0.06329617834394904</v>
+        <v>0.03545493378897907</v>
       </c>
       <c r="R3">
-        <v>0.4984326018808778</v>
+        <v>0.3014527845036319</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>313.1</v>
+        <v>349.7</v>
       </c>
       <c r="V3">
-        <v>0.6232085987261147</v>
+        <v>0.4979353552612844</v>
       </c>
       <c r="W3">
-        <v>0.1229523993062247</v>
+        <v>0.1827029418270294</v>
       </c>
       <c r="X3">
-        <v>0.08702399111590897</v>
+        <v>0.07499027415206808</v>
       </c>
       <c r="Y3">
-        <v>0.03592840819031573</v>
+        <v>0.1077126676749613</v>
       </c>
       <c r="Z3">
-        <v>4.606168542054562</v>
+        <v>4.37410790750785</v>
       </c>
       <c r="AA3">
-        <v>0.3711541261355211</v>
+        <v>0.574698164625387</v>
       </c>
       <c r="AB3">
-        <v>0.08692764012713726</v>
+        <v>0.07495975454523755</v>
       </c>
       <c r="AC3">
-        <v>0.2842264860083838</v>
+        <v>0.4997384100801495</v>
       </c>
       <c r="AD3">
-        <v>1.12</v>
+        <v>0.636</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.12</v>
+        <v>0.636</v>
       </c>
       <c r="AG3">
-        <v>-311.98</v>
+        <v>-349.064</v>
       </c>
       <c r="AH3">
-        <v>0.002224340641881157</v>
+        <v>0.0009047765372665507</v>
       </c>
       <c r="AI3">
-        <v>0.002471206036803319</v>
+        <v>0.001228900018549434</v>
       </c>
       <c r="AJ3">
-        <v>-1.638378321604874</v>
+        <v>-0.9881891992888606</v>
       </c>
       <c r="AK3">
-        <v>-2.226520125606623</v>
+        <v>-2.0797921780786</v>
       </c>
       <c r="AL3">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AM3">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AN3">
-        <v>0.01904761904761905</v>
+        <v>0.006417759838546923</v>
       </c>
       <c r="AO3">
-        <v>2465.217391304348</v>
+        <v>4413.636363636364</v>
       </c>
       <c r="AP3">
-        <v>-5.305782312925171</v>
+        <v>-3.52234106962664</v>
       </c>
       <c r="AQ3">
-        <v>2465.217391304348</v>
+        <v>4413.636363636364</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Taiwan Fire &amp; Marine Insurance Co., Ltd. (TWSE:2832)</t>
+          <t>Union Insurance Co., Ltd. (TWSE:2816)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0464</v>
+        <v>0.0607</v>
       </c>
       <c r="E4">
-        <v>0.0605</v>
+        <v>-0.0535</v>
       </c>
       <c r="G4">
-        <v>0.08455696202531646</v>
+        <v>-0.1303265940902022</v>
       </c>
       <c r="H4">
-        <v>0.08455696202531646</v>
+        <v>-0.1303265940902022</v>
       </c>
       <c r="I4">
-        <v>0.1893670886075949</v>
+        <v>0.05723172628304821</v>
       </c>
       <c r="J4">
-        <v>0.1553792691664676</v>
+        <v>0.05129200117691563</v>
       </c>
       <c r="K4">
-        <v>34.7</v>
+        <v>16.6</v>
       </c>
       <c r="L4">
-        <v>0.1756962025316456</v>
+        <v>0.05163297045101089</v>
       </c>
       <c r="M4">
-        <v>8.550000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03546246370800498</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.2463976945244957</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>8.550000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03546246370800498</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2463976945244957</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>106.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="V4">
-        <v>0.4413106594773953</v>
+        <v>0.3407942238267148</v>
       </c>
       <c r="W4">
-        <v>0.1016403046280024</v>
+        <v>0.09993979530403373</v>
       </c>
       <c r="X4">
-        <v>0.08719689962759444</v>
+        <v>0.07502747222479424</v>
       </c>
       <c r="Y4">
-        <v>0.01444340500040792</v>
+        <v>0.02491232307923949</v>
       </c>
       <c r="Z4">
-        <v>1.076059714503651</v>
+        <v>4.117202607348215</v>
       </c>
       <c r="AA4">
-        <v>0.167197372019055</v>
+        <v>0.2111795609817048</v>
       </c>
       <c r="AB4">
-        <v>0.08690663476483718</v>
+        <v>0.07496380169601077</v>
       </c>
       <c r="AC4">
-        <v>0.08029073725421787</v>
+        <v>0.136215759285694</v>
       </c>
       <c r="AD4">
-        <v>1.62</v>
+        <v>0.607</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>0.607</v>
       </c>
       <c r="AG4">
-        <v>-104.78</v>
+        <v>-93.79300000000001</v>
       </c>
       <c r="AH4">
-        <v>0.006674357284113382</v>
+        <v>0.00218654428742791</v>
       </c>
       <c r="AI4">
-        <v>0.005190311418685122</v>
+        <v>0.003300581272055984</v>
       </c>
       <c r="AJ4">
-        <v>-0.7686326291079812</v>
+        <v>-0.5119509625723908</v>
       </c>
       <c r="AK4">
-        <v>-0.5093330740812755</v>
+        <v>-1.047884522998201</v>
       </c>
       <c r="AL4">
-        <v>0.051</v>
+        <v>0.201</v>
       </c>
       <c r="AM4">
-        <v>0.051</v>
+        <v>0.201</v>
       </c>
       <c r="AN4">
-        <v>0.04229765013054831</v>
+        <v>0.03004950495049505</v>
       </c>
       <c r="AO4">
-        <v>733.3333333333334</v>
+        <v>91.54228855721392</v>
       </c>
       <c r="AP4">
-        <v>-2.735770234986945</v>
+        <v>-4.643217821782179</v>
       </c>
       <c r="AQ4">
-        <v>733.3333333333334</v>
+        <v>91.54228855721392</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The First Insurance Co., Ltd. (TWSE:2852)</t>
+          <t>Taiwan Fire &amp; Marine Insurance Co., Ltd. (TWSE:2832)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,46 +987,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0299</v>
+        <v>0.0559</v>
       </c>
       <c r="E5">
-        <v>0.0256</v>
+        <v>0.0624</v>
       </c>
       <c r="G5">
-        <v>0.1174825174825175</v>
+        <v>0.1198428290766208</v>
       </c>
       <c r="H5">
-        <v>0.1174825174825175</v>
+        <v>0.1198428290766208</v>
       </c>
       <c r="I5">
-        <v>0.09324009324009325</v>
+        <v>0.1645383104125737</v>
       </c>
       <c r="J5">
-        <v>0.07838626020444203</v>
+        <v>0.1343729535036018</v>
       </c>
       <c r="K5">
-        <v>19.4</v>
+        <v>28</v>
       </c>
       <c r="L5">
-        <v>0.09044289044289043</v>
+        <v>0.137524557956778</v>
       </c>
       <c r="M5">
-        <v>14.8</v>
+        <v>11.3</v>
       </c>
       <c r="N5">
-        <v>0.09554551323434474</v>
+        <v>0.03593004769475358</v>
       </c>
       <c r="O5">
-        <v>0.7628865979381444</v>
+        <v>0.4035714285714286</v>
       </c>
       <c r="P5">
-        <v>14.8</v>
+        <v>11.3</v>
       </c>
       <c r="Q5">
-        <v>0.09554551323434474</v>
+        <v>0.03593004769475358</v>
       </c>
       <c r="R5">
-        <v>0.7628865979381444</v>
+        <v>0.4035714285714286</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1038,73 +1035,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>57.5</v>
+        <v>99.3</v>
       </c>
       <c r="V5">
-        <v>0.3712072304712718</v>
+        <v>0.3157392686804452</v>
       </c>
       <c r="W5">
-        <v>0.07501933488012373</v>
+        <v>0.09017713365539452</v>
       </c>
       <c r="X5">
-        <v>0.08697841533708447</v>
+        <v>0.07515725582189356</v>
       </c>
       <c r="Y5">
-        <v>-0.01195908045696074</v>
+        <v>0.01501987783350096</v>
       </c>
       <c r="Z5">
-        <v>1.09998871806443</v>
+        <v>0.9896947307019249</v>
       </c>
       <c r="AA5">
-        <v>0.08622400187614904</v>
+        <v>0.1329882040313695</v>
       </c>
       <c r="AB5">
-        <v>0.08693320816644445</v>
+        <v>0.07493240702330349</v>
       </c>
       <c r="AC5">
-        <v>-0.0007092062902954166</v>
+        <v>0.05805579700806603</v>
       </c>
       <c r="AD5">
-        <v>0.162</v>
+        <v>2.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.162</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>-57.338</v>
+        <v>-97.2</v>
       </c>
       <c r="AH5">
-        <v>0.001044743392965394</v>
+        <v>0.006632975363234365</v>
       </c>
       <c r="AI5">
-        <v>0.0007011105244479836</v>
+        <v>0.006174654513378418</v>
       </c>
       <c r="AJ5">
-        <v>-0.5877083290625448</v>
+        <v>-0.4473078693051081</v>
       </c>
       <c r="AK5">
-        <v>-0.3303603323308097</v>
+        <v>-0.4036544850498339</v>
       </c>
       <c r="AL5">
-        <v>0.005</v>
+        <v>0.053</v>
       </c>
       <c r="AM5">
-        <v>0.005</v>
+        <v>0.053</v>
       </c>
       <c r="AN5">
-        <v>0.007751196172248805</v>
+        <v>0.06104651162790698</v>
       </c>
       <c r="AO5">
-        <v>4000</v>
+        <v>632.0754716981132</v>
       </c>
       <c r="AP5">
-        <v>-2.743444976076555</v>
+        <v>-2.825581395348837</v>
       </c>
       <c r="AQ5">
-        <v>4000</v>
+        <v>632.0754716981132</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Union Insurance Co., Ltd. (TWSE:2816)</t>
+          <t>The First Insurance Co., Ltd. (TWSE:2852)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,43 +1121,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0367</v>
+        <v>0.0287</v>
+      </c>
+      <c r="E6">
+        <v>-0.0283</v>
       </c>
       <c r="G6">
-        <v>0.1160949868073879</v>
+        <v>0.0899731423455685</v>
       </c>
       <c r="H6">
-        <v>0.1160949868073879</v>
+        <v>0.0899731423455685</v>
       </c>
       <c r="I6">
-        <v>-0.05767056162834527</v>
+        <v>0.08907788719785138</v>
       </c>
       <c r="J6">
-        <v>-0.05767056162834527</v>
+        <v>0.07409660616912182</v>
       </c>
       <c r="K6">
-        <v>-15.7</v>
+        <v>16.5</v>
       </c>
       <c r="L6">
-        <v>-0.05917828872973991</v>
+        <v>0.0738585496866607</v>
       </c>
       <c r="M6">
-        <v>7.03</v>
+        <v>6.74</v>
       </c>
       <c r="N6">
-        <v>0.0611304347826087</v>
+        <v>0.03697202413603949</v>
       </c>
       <c r="O6">
-        <v>-0.4477707006369427</v>
+        <v>0.4084848484848485</v>
       </c>
       <c r="P6">
-        <v>7.03</v>
+        <v>6.74</v>
       </c>
       <c r="Q6">
-        <v>0.0611304347826087</v>
+        <v>0.03697202413603949</v>
       </c>
       <c r="R6">
-        <v>-0.4477707006369427</v>
+        <v>0.4084848484848485</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1169,73 +1169,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>88.5</v>
+        <v>49.7</v>
       </c>
       <c r="V6">
-        <v>0.7695652173913043</v>
+        <v>0.2726275370268788</v>
       </c>
       <c r="W6">
-        <v>-0.07208448117539026</v>
+        <v>0.07145950627977479</v>
       </c>
       <c r="X6">
-        <v>0.08710122330195505</v>
+        <v>0.07499121205613452</v>
       </c>
       <c r="Y6">
-        <v>-0.1591857044773453</v>
+        <v>-0.003531705776359723</v>
       </c>
       <c r="Z6">
-        <v>1.935140339616036</v>
+        <v>1.28714810845692</v>
       </c>
       <c r="AA6">
-        <v>-0.1116006302153236</v>
+        <v>0.09537330647366252</v>
       </c>
       <c r="AB6">
-        <v>0.08691823455485689</v>
+        <v>0.07495960005868714</v>
       </c>
       <c r="AC6">
-        <v>-0.1985188647701805</v>
+        <v>0.02041370641497538</v>
       </c>
       <c r="AD6">
-        <v>0.487</v>
+        <v>0.171</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.487</v>
+        <v>0.171</v>
       </c>
       <c r="AG6">
-        <v>-88.01300000000001</v>
+        <v>-49.529</v>
       </c>
       <c r="AH6">
-        <v>0.004216924848684267</v>
+        <v>0.0009371352160069272</v>
       </c>
       <c r="AI6">
-        <v>0.002923397383949528</v>
+        <v>0.0006980418090304567</v>
       </c>
       <c r="AJ6">
-        <v>-3.261311001593361</v>
+        <v>-0.3730407995721957</v>
       </c>
       <c r="AK6">
-        <v>-1.12711462855533</v>
+        <v>-0.253642373931613</v>
       </c>
       <c r="AL6">
-        <v>0.216</v>
+        <v>0.008</v>
       </c>
       <c r="AM6">
-        <v>0.216</v>
+        <v>0.008</v>
       </c>
       <c r="AN6">
-        <v>-0.03580882352941177</v>
+        <v>0.008221153846153847</v>
       </c>
       <c r="AO6">
-        <v>-70.83333333333334</v>
+        <v>2487.5</v>
       </c>
       <c r="AP6">
-        <v>6.471544117647059</v>
+        <v>-2.381201923076923</v>
       </c>
       <c r="AQ6">
-        <v>-70.83333333333334</v>
+        <v>2487.5</v>
       </c>
     </row>
   </sheetData>
